--- a/docs/downloads/05/tbl_cooking_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_mangabe.xlsx
@@ -423,12 +423,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -458,12 +452,6 @@
         <is>
           <t>Gaz</t>
         </is>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.2</v>
       </c>
     </row>
     <row r="7">

--- a/docs/downloads/05/tbl_cooking_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_mangabe.xlsx
@@ -391,7 +391,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>26.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C3">
         <v>70</v>
       </c>
       <c r="D3">
-        <v>73.7</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -439,7 +439,7 @@
         <v>218</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -462,14 +462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C7">
         <v>420</v>
       </c>
       <c r="D7">
-        <v>65.5</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>
